--- a/tasks/finalpool/budget-variance-analysis-quarterly/groundtruth_workspace/variance_analysis.xlsx
+++ b/tasks/finalpool/budget-variance-analysis-quarterly/groundtruth_workspace/variance_analysis.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,43 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00366092"/>
-        <bgColor rgb="00366092"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,13 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,61 +415,52 @@
   </sheetPr>
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Q3 Budget Variance Analysis</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Q1 FY2024 Budget Variance Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Cost Center</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Dept</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Budget YTD</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Actual YTD</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Q1 Budget</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Q1 Actual</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Variance $</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Variance %</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -525,18 +481,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1800000</v>
+        <v>600000</v>
       </c>
       <c r="E4" t="n">
-        <v>1785000</v>
+        <v>585000</v>
       </c>
       <c r="F4" t="n">
         <v>-15000</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+        <v>-2.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Favorable</t>
         </is>
@@ -557,18 +513,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>360000</v>
+        <v>120000</v>
       </c>
       <c r="E5" t="n">
-        <v>372000</v>
+        <v>126000</v>
       </c>
       <c r="F5" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
@@ -589,18 +545,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>180000</v>
+        <v>60000</v>
       </c>
       <c r="E6" t="n">
-        <v>198000</v>
+        <v>63000</v>
       </c>
       <c r="F6" t="n">
-        <v>18000</v>
+        <v>3000</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
@@ -621,10 +577,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1350000</v>
+        <v>450000</v>
       </c>
       <c r="E7" t="n">
-        <v>1350000</v>
+        <v>450000</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -653,18 +609,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>675000</v>
+        <v>225000</v>
       </c>
       <c r="E8" t="n">
-        <v>742500</v>
+        <v>240000</v>
       </c>
       <c r="F8" t="n">
-        <v>67500</v>
+        <v>15000</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+        <v>6.7</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
@@ -685,18 +641,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>270000</v>
+        <v>90000</v>
       </c>
       <c r="E9" t="n">
-        <v>261000</v>
+        <v>85500</v>
       </c>
       <c r="F9" t="n">
-        <v>-9000</v>
+        <v>-4500</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Favorable</t>
         </is>
@@ -717,10 +673,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="E10" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -749,18 +705,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>900000</v>
+        <v>300000</v>
       </c>
       <c r="E11" t="n">
-        <v>945000</v>
+        <v>315000</v>
       </c>
       <c r="F11" t="n">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
@@ -781,20 +737,20 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="E12" t="n">
-        <v>600000</v>
+        <v>195000</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>On Budget</t>
+          <t>Favorable</t>
         </is>
       </c>
     </row>
@@ -813,25 +769,27 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="E13" t="n">
-        <v>315000</v>
+        <v>105000</v>
       </c>
       <c r="F13" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Summary Metrics</t>
         </is>
@@ -840,23 +798,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Total Budget YTD</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>SUM(D4:D13)</f>
-        <v/>
+          <t>Total Q1 Budget</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2295000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Total Actual YTD</t>
-        </is>
-      </c>
-      <c r="B18">
-        <f>SUM(E4:E13)</f>
-        <v/>
+          <t>Total Q1 Actual</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2314500</v>
       </c>
     </row>
     <row r="19">
@@ -865,9 +821,8 @@
           <t>Total Variance</t>
         </is>
       </c>
-      <c r="B19">
-        <f>B18-B17</f>
-        <v/>
+      <c r="B19" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="20">
@@ -876,15 +831,11 @@
           <t>Overall Variance %</t>
         </is>
       </c>
-      <c r="B20">
-        <f>B19/B17</f>
-        <v/>
+      <c r="B20" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>